--- a/data.mn/public/datasets/mongolbank-total-bank-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-total-bank-loans.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2325,4 +2326,1924 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B190"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>огноо</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>нийт_зээл_тэрбум_төгрөг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2000-03-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>50.263</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2000-06-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54.235</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2000-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.926</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>63.766</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>77.322</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>92.723</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2001-09-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>96.723</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2001-12-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>127.484</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2002-03-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>151.143</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2002-06-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>191.041</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2002-09-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>196.615</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2002-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>231.45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>279.924</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2003-06-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>327.926</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2003-09-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>352.124</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2003-12-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>441.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>486.592</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>525.458</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>565.794</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>606.178</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>640.266</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>719.742</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>774.2380000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>859.449</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>955.112</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1051.062</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1113.506</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1222.342</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1403.762</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1599.162</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1861.356</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2055.278</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2335.622</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2558.879</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2714.569</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2635.128</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2670.872</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2557.725</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2630.564</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2734.817</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2849.058</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3050.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3228.171</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3696.26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4517.281</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5018.953</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5597.744</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5741.474</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6266.015</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6819.411</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6941.135</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7336.37</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>8553.474</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10098.617</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10715.633</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>11332.387</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>12241.976</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>12551.159</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>12440.926</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>12210.964</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>11881.968</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>11873.148</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>11633.574</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>11764.55</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>11566.291</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>11370.374</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>11949.791</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>12023.957</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>12359.511</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>12409.421</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>12484.509</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>12633.769</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>12337.509</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>12294.768</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>12498.632</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>12593.147</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>12621.792</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>12613.829</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>12805.394</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>12940.703</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>13160.054</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>13316.647</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>13281.674</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>13389.665</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>13506.743</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>13548.042</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>13718.925</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>14033.03</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>14355.814</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>14859.731</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>15277.098</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>15469.585</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>15807.226</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>16206.667</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>16312.447</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>16575.583</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>17082.386</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>17076.162</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>17104.156</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>17327.282</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>17510.101</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>17824.283</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>18061.496</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>18122.812</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>18099.812</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>17994.565</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>18038.924</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>18004.867</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>17932.249</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>17918.66</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>17189.444</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>16988.561</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>16996.075</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>17012.761</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>17200.17</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>17159.657</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>17212.957</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>17182.055</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>17042.921</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>16828.618</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>17034.236</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>17059.364</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>16972.923</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>17467.086</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>17487.066</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>18067.142</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>18966.107</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>19263.061</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>19689.945</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>20018.192</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>19875.979</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>20049.344</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>20667.355</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>20797.001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>21075.44</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>21872.392</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>22543.517</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>23045.771</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>23250.557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>23113.782</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>22562.016</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>22757.123</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>22583.1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>22447.818</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>22008.274</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>22268.116</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>22409.057</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>23012.94</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>23489.272</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>24290.684</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>25355.145</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>25143.826</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>25608.608</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>25871.065</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>26122.711</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>26638.746</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>27151.617</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>27508.943</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>27830.246</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>28923.657</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>29699.999</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>31144.651</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>33258.646</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>33224.172</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>34223.757</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>34983.032</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>35167.347</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>35612.977</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>36781.473</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>37123.988</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>38397.359</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>38600.733</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>39530.298</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>40344.608</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>42224.382</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>42360.924</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>42294.729</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>42726.783</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>43460.369</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>43107.326</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>43751.57</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>43908.126</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>43889.722</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>45005.551</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>45963.701</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>47259.969</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>48957.222</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>47876.124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/mongolbank-total-bank-loans.xlsx
+++ b/data.mn/public/datasets/mongolbank-total-bank-loans.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2321,26 @@
       </c>
       <c r="B190" t="n">
         <v>47876.124</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>48362.142</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>49324.959</v>
       </c>
     </row>
   </sheetData>
@@ -2334,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4243,6 +4263,26 @@
         <v>47876.124</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>48362.142</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>49324.959</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
